--- a/J1.xlsx
+++ b/J1.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Session : </t>
   </si>
   <si>
-    <t>Session 1</t>
+    <t>Session A</t>
   </si>
   <si>
     <r>
@@ -86,7 +86,7 @@
     </r>
   </si>
   <si>
-    <t>Dupont</t>
+    <t>Doe</t>
   </si>
   <si>
     <r>
@@ -108,13 +108,13 @@
     </r>
   </si>
   <si>
-    <t>Jean</t>
+    <t>John</t>
   </si>
   <si>
     <t>Date de l'évaluation :</t>
   </si>
   <si>
-    <t>2024-12-23</t>
+    <t>2024-12-31</t>
   </si>
   <si>
     <t>Lieu de l'évaluation (entreprise ou centre de formation) :</t>
@@ -4235,7 +4235,7 @@
         <v>112</v>
       </c>
       <c r="G16" s="130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H16" s="70" t="s">
         <v>113</v>
